--- a/Result/profitability/1568.xlsx
+++ b/Result/profitability/1568.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM65"/>
+  <dimension ref="A1:AM66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.28625</v>
+        <v>0.32125</v>
       </c>
       <c r="N2" t="n">
-        <v>30.28625</v>
+        <v>32.04499999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.26875</v>
+        <v>0.305</v>
       </c>
       <c r="N3" t="n">
-        <v>29.65125</v>
+        <v>30.78375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-2.12</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.02999999999999997</v>
+        <v>-0.02625</v>
       </c>
       <c r="N4" t="n">
-        <v>24.86125</v>
+        <v>25.2225</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.63</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.175</v>
+        <v>-0.10625</v>
       </c>
       <c r="N5" t="n">
-        <v>21.35375</v>
+        <v>21.91375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.21</v>
+        <v>-0.1825</v>
       </c>
       <c r="N6" t="n">
-        <v>19.2125</v>
+        <v>20.4325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.32125</v>
+        <v>-0.31125</v>
       </c>
       <c r="N7" t="n">
-        <v>17.0525</v>
+        <v>17.4075</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8687,6 +8687,133 @@
       </c>
       <c r="AM65" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>305</v>
+      </c>
+      <c r="D66" t="n">
+        <v>191</v>
+      </c>
+      <c r="E66" t="n">
+        <v>114</v>
+      </c>
+      <c r="F66" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="G66" t="n">
+        <v>68</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>22.30%</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="n">
+        <v>71</v>
+      </c>
+      <c r="K66" t="n">
+        <v>58</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="N66" t="n">
+        <v>31.8575</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.09803921568627461</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0.2800000000000011</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.00756756756756749</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>4.480000000000004</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.1365853658536587</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
